--- a/case_studies/high_feedstock_availability_5_dd/2030/technologies.xlsx
+++ b/case_studies/high_feedstock_availability_5_dd/2030/technologies.xlsx
@@ -691,10 +691,10 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>53.53</v>
+        <v>24.29</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>150.56</v>
+        <v>89.61</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0</v>
@@ -712,28 +712,28 @@
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>135.49</v>
+        <v>61.5</v>
       </c>
       <c r="Q2" s="3" t="n">
         <v>184.21</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>36.8</v>
+        <v>16.7</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>22.37</v>
+        <v>42.53</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>159.94</v>
+        <v>282.2</v>
       </c>
       <c r="U2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>49.16</v>
+        <v>186.92</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>23.43</v>
+        <v>0</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>0</v>
+        <v>34.14</v>
       </c>
       <c r="AA2" s="3" t="n">
         <v>0</v>
@@ -779,10 +779,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>8.08</v>
+        <v>16.16</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>0.32</v>
@@ -794,7 +794,7 @@
         <v>35.39</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>32.33</v>
+        <v>63.6</v>
       </c>
       <c r="L3" s="5" t="n">
         <v>0</v>
@@ -821,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="T3" s="5" t="n">
-        <v>17.75</v>
+        <v>33.91</v>
       </c>
       <c r="U3" s="5" t="n">
         <v>0</v>
@@ -879,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>7.07</v>
+        <v>14.14</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>153.06</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>20.3</v>
+        <v>40.6</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>0</v>
@@ -909,16 +909,16 @@
         <v>31.96</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>63.68</v>
+        <v>127.37</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>43.32</v>
+        <v>86.64</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>231.42</v>
+        <v>446.54</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0</v>
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>27.91</v>
+        <v>55.82</v>
       </c>
       <c r="AA4" s="3" t="n">
         <v>0</v>
@@ -973,10 +973,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>38.39</v>
+        <v>2038.39</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>0</v>
@@ -988,7 +988,7 @@
         <v>241.1</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>148.52</v>
+        <v>280.97</v>
       </c>
       <c r="L5" s="5" t="n">
         <v>0</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>125.97</v>
+        <v>234.67</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>0</v>
+        <v>11516.9</v>
       </c>
       <c r="V5" s="5" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="Z5" s="5" t="n">
-        <v>204.22</v>
+        <v>386.34</v>
       </c>
       <c r="AA5" s="5" t="n">
         <v>0</v>
@@ -1064,28 +1064,28 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>62.79</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>55.06</v>
+        <v>67.03</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>141.59</v>
+        <v>116.38</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>57.57</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>0</v>
@@ -1100,19 +1100,19 @@
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>139.37</v>
+        <v>119.48</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>139.37</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>37.86</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0</v>
+        <v>13.53</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>95.54000000000001</v>
+        <v>162.57</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>0</v>
@@ -1121,7 +1121,7 @@
         <v>0</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>37.86</v>
+        <v>0</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>0</v>
@@ -1130,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0</v>
+        <v>59.12</v>
       </c>
       <c r="AA6" s="3" t="n">
         <v>0</v>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>0</v>
@@ -1203,22 +1203,22 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>18.48</v>
+        <v>19.82</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>15.14</v>
+        <v>15.67</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>48.52</v>
+        <v>77.63</v>
       </c>
       <c r="U7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>0.36</v>
+        <v>1.43</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>18.38</v>
+        <v>19.43</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>58.91</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>160.06</v>
+        <v>143.3</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1285,37 +1285,37 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>386.97</v>
+        <v>653.27</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>386.97</v>
+        <v>653.27</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>165.54</v>
+        <v>149.13</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>219.98</v>
+        <v>251.68</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>44.97</v>
+        <v>40.51</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>36.8</v>
+        <v>68.88</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>110.4</v>
+        <v>1352.44</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>0</v>
+        <v>11300</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>1.07</v>
+        <v>4.02</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>44.67</v>
+        <v>39.41</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>0</v>

--- a/case_studies/high_feedstock_availability_5_dd/2030/technologies.xlsx
+++ b/case_studies/high_feedstock_availability_5_dd/2030/technologies.xlsx
@@ -724,7 +724,7 @@
         <v>42.53</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>282.2</v>
+        <v>159.94</v>
       </c>
       <c r="U2" s="3" t="n">
         <v>0</v>
@@ -779,10 +779,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>16.16</v>
+        <v>8.08</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>0.32</v>
@@ -794,7 +794,7 @@
         <v>35.39</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>63.6</v>
+        <v>32.33</v>
       </c>
       <c r="L3" s="5" t="n">
         <v>0</v>
@@ -821,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="T3" s="5" t="n">
-        <v>33.91</v>
+        <v>17.75</v>
       </c>
       <c r="U3" s="5" t="n">
         <v>0</v>
@@ -879,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>14.14</v>
+        <v>7.07</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>153.06</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>40.6</v>
+        <v>20.3</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>0</v>
@@ -918,7 +918,7 @@
         <v>86.64</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>446.54</v>
+        <v>231.42</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0</v>
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>55.82</v>
+        <v>27.91</v>
       </c>
       <c r="AA4" s="3" t="n">
         <v>0</v>
@@ -973,10 +973,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>2038.39</v>
+        <v>38.39</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>0</v>
@@ -988,7 +988,7 @@
         <v>241.1</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>280.97</v>
+        <v>148.52</v>
       </c>
       <c r="L5" s="5" t="n">
         <v>0</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>234.67</v>
+        <v>125.97</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>11516.9</v>
+        <v>0</v>
       </c>
       <c r="V5" s="5" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="Z5" s="5" t="n">
-        <v>386.34</v>
+        <v>204.22</v>
       </c>
       <c r="AA5" s="5" t="n">
         <v>0</v>
@@ -1067,13 +1067,13 @@
         <v>62.79</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>22.22</v>
+        <v>11.11</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0</v>
@@ -1085,7 +1085,7 @@
         <v>116.38</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>57.57</v>
+        <v>42.99</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>0</v>
@@ -1112,7 +1112,7 @@
         <v>13.53</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>162.57</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>0</v>
@@ -1170,13 +1170,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>48.52</v>
+        <v>23.07</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>59.3</v>
@@ -1203,13 +1203,13 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>19.82</v>
+        <v>15.86</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>15.67</v>
+        <v>25.97</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>77.63</v>
+        <v>48.52</v>
       </c>
       <c r="U7" s="5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>1.43</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>19.43</v>
+        <v>15.47</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>58.91</v>
+        <v>60.46</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>143.3</v>
+        <v>147.09</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1294,28 +1294,28 @@
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>149.13</v>
+        <v>153.04</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>251.68</v>
+        <v>244.11</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>40.51</v>
+        <v>41.57</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>68.88</v>
+        <v>61.07</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>1352.44</v>
+        <v>110.4</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>11300</v>
+        <v>0</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>4.02</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>39.41</v>
+        <v>40.48</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>0</v>

--- a/case_studies/high_feedstock_availability_5_dd/2030/technologies.xlsx
+++ b/case_studies/high_feedstock_availability_5_dd/2030/technologies.xlsx
@@ -691,10 +691,10 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>24.29</v>
+        <v>51.54</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>89.61</v>
+        <v>140.61</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0</v>
@@ -712,16 +712,16 @@
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>61.5</v>
+        <v>130.46</v>
       </c>
       <c r="Q2" s="3" t="n">
         <v>184.21</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>16.7</v>
+        <v>35.44</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>42.53</v>
+        <v>21.27</v>
       </c>
       <c r="T2" s="3" t="n">
         <v>159.94</v>
@@ -730,10 +730,10 @@
         <v>0</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>186.92</v>
+        <v>69.83</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>0</v>
+        <v>16.44</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>34.14</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="3" t="n">
         <v>0</v>
@@ -909,13 +909,13 @@
         <v>31.96</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>127.37</v>
+        <v>63.68</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>86.64</v>
+        <v>43.32</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>231.42</v>
@@ -1079,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>67.03</v>
+        <v>67.83</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>116.38</v>
+        <v>117.43</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>42.99</v>
@@ -1100,16 +1100,16 @@
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>119.48</v>
+        <v>121.61</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>139.37</v>
+        <v>135.45</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>13.53</v>
+        <v>9.42</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>95.54000000000001</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>23.07</v>
+        <v>48.52</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>59.3</v>
@@ -1203,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>15.86</v>
+        <v>19.87</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>25.97</v>
+        <v>15.58</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>48.52</v>
@@ -1215,10 +1215,10 @@
         <v>0</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>15.47</v>
+        <v>19.4</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>60.46</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>147.09</v>
+        <v>166.47</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>153.04</v>
+        <v>171.53</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>244.11</v>
+        <v>208.42</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>41.57</v>
+        <v>46.59</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>61.07</v>
+        <v>25.1</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>110.4</v>
@@ -1312,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>40.48</v>
+        <v>46.59</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>0</v>

--- a/case_studies/high_feedstock_availability_5_dd/2030/technologies.xlsx
+++ b/case_studies/high_feedstock_availability_5_dd/2030/technologies.xlsx
@@ -691,10 +691,10 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>51.54</v>
+        <v>12.45</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>140.61</v>
+        <v>78.39</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0</v>
@@ -712,16 +712,16 @@
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>130.46</v>
+        <v>31.52</v>
       </c>
       <c r="Q2" s="3" t="n">
         <v>184.21</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>35.44</v>
+        <v>8.56</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>21.27</v>
+        <v>42.53</v>
       </c>
       <c r="T2" s="3" t="n">
         <v>159.94</v>
@@ -730,10 +730,10 @@
         <v>0</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>69.83</v>
+        <v>280.02</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>16.44</v>
+        <v>0</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>0</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AA2" s="3" t="n">
         <v>0</v>
@@ -909,13 +909,13 @@
         <v>31.96</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>63.68</v>
+        <v>127.37</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>43.32</v>
+        <v>86.64</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>231.42</v>
@@ -1079,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>67.83</v>
+        <v>67.03</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>117.43</v>
+        <v>116.38</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>42.99</v>
@@ -1100,16 +1100,16 @@
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>121.61</v>
+        <v>119.48</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>135.45</v>
+        <v>139.37</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>9.42</v>
+        <v>13.53</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>95.54000000000001</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>48.52</v>
+        <v>22.98</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>59.3</v>
@@ -1203,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>19.87</v>
+        <v>15.8</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>15.58</v>
+        <v>25.97</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>48.52</v>
@@ -1215,10 +1215,10 @@
         <v>0</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>19.4</v>
+        <v>15.21</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>67.76000000000001</v>
+        <v>60.37</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>166.47</v>
+        <v>146.27</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>171.53</v>
+        <v>152.82</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>208.42</v>
+        <v>244.55</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>46.59</v>
+        <v>41.51</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>25.1</v>
+        <v>61.07</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>110.4</v>
@@ -1312,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>0</v>
+        <v>6.08</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>46.59</v>
+        <v>39.85</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>0</v>
